--- a/docs/excel/Inventari Excel Template.xlsx
+++ b/docs/excel/Inventari Excel Template.xlsx
@@ -451,7 +451,6 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2494,9 +2493,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="J1:N1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
